--- a/tests/agent_contract/data/M4_marketing_roi.xlsx
+++ b/tests/agent_contract/data/M4_marketing_roi.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,53 +413,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G152"/>
+  <dimension ref="A1:H151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n"/>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>渠道名称</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>投放日期</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>投放金额</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>曝光量</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>点击量</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>转化量</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>销售额</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ROI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>渠道名称</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>投放日期</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>投放金额</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>曝光量</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>点击量</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>转化量</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>销售额</t>
-        </is>
+          <t>2024-07-01</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14112</v>
+      </c>
+      <c r="D2" t="n">
+        <v>213446</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5394</v>
+      </c>
+      <c r="F2" t="n">
+        <v>235</v>
+      </c>
+      <c r="G2" t="n">
+        <v>73085</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5.1789</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -472,25 +500,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13485</v>
+        <v>12475</v>
       </c>
       <c r="D3" t="n">
-        <v>255395</v>
+        <v>787973</v>
       </c>
       <c r="E3" t="n">
-        <v>5426</v>
+        <v>9381</v>
       </c>
       <c r="F3" t="n">
-        <v>189</v>
+        <v>285</v>
       </c>
       <c r="G3" t="n">
-        <v>64827</v>
+        <v>74385</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5.9627</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -499,25 +530,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13938</v>
+        <v>12705</v>
       </c>
       <c r="D4" t="n">
-        <v>976209</v>
+        <v>471818</v>
       </c>
       <c r="E4" t="n">
-        <v>10848</v>
+        <v>7945</v>
       </c>
       <c r="F4" t="n">
-        <v>320</v>
+        <v>268</v>
       </c>
       <c r="G4" t="n">
-        <v>91520</v>
+        <v>94604</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.4462</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -526,25 +560,28 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>12530</v>
+        <v>7950</v>
       </c>
       <c r="D5" t="n">
-        <v>499958</v>
+        <v>142096</v>
       </c>
       <c r="E5" t="n">
-        <v>6105</v>
+        <v>2413</v>
       </c>
       <c r="F5" t="n">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="G5" t="n">
-        <v>76544</v>
+        <v>43260</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.4415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -553,52 +590,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9268</v>
+        <v>12161</v>
       </c>
       <c r="D6" t="n">
-        <v>196493</v>
+        <v>316698</v>
       </c>
       <c r="E6" t="n">
-        <v>3625</v>
+        <v>7392</v>
       </c>
       <c r="F6" t="n">
-        <v>175</v>
+        <v>288</v>
       </c>
       <c r="G6" t="n">
-        <v>84875</v>
+        <v>109440</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.9993</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-07-01</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>14243</v>
+        <v>12625</v>
       </c>
       <c r="D7" t="n">
-        <v>368810</v>
+        <v>298723</v>
       </c>
       <c r="E7" t="n">
-        <v>6331</v>
+        <v>3296</v>
       </c>
       <c r="F7" t="n">
-        <v>234</v>
+        <v>221</v>
       </c>
       <c r="G7" t="n">
-        <v>115830</v>
+        <v>97903</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.7547</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,25 +650,28 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>13284</v>
+        <v>17179</v>
       </c>
       <c r="D8" t="n">
-        <v>164279</v>
+        <v>888946</v>
       </c>
       <c r="E8" t="n">
-        <v>5490</v>
+        <v>9258</v>
       </c>
       <c r="F8" t="n">
-        <v>159</v>
+        <v>270</v>
       </c>
       <c r="G8" t="n">
-        <v>49131</v>
+        <v>100170</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.831</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -634,25 +680,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19204</v>
+        <v>10746</v>
       </c>
       <c r="D9" t="n">
-        <v>993374</v>
+        <v>511965</v>
       </c>
       <c r="E9" t="n">
-        <v>9628</v>
+        <v>9460</v>
       </c>
       <c r="F9" t="n">
-        <v>364</v>
+        <v>214</v>
       </c>
       <c r="G9" t="n">
-        <v>105924</v>
+        <v>90094</v>
+      </c>
+      <c r="H9" t="n">
+        <v>8.384</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -661,25 +710,28 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>13357</v>
+        <v>6871</v>
       </c>
       <c r="D10" t="n">
-        <v>307432</v>
+        <v>140379</v>
       </c>
       <c r="E10" t="n">
-        <v>6405</v>
+        <v>3578</v>
       </c>
       <c r="F10" t="n">
-        <v>324</v>
+        <v>128</v>
       </c>
       <c r="G10" t="n">
-        <v>104976</v>
+        <v>69760</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.1528</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -688,52 +740,58 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>7046</v>
+        <v>13282</v>
       </c>
       <c r="D11" t="n">
-        <v>118853</v>
+        <v>224078</v>
       </c>
       <c r="E11" t="n">
-        <v>2516</v>
+        <v>5075</v>
       </c>
       <c r="F11" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G11" t="n">
-        <v>90992</v>
+        <v>80840</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.0864</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-07-03</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9984</v>
+        <v>9290</v>
       </c>
       <c r="D12" t="n">
-        <v>266154</v>
+        <v>243099</v>
       </c>
       <c r="E12" t="n">
-        <v>7375</v>
+        <v>4682</v>
       </c>
       <c r="F12" t="n">
-        <v>273</v>
+        <v>299</v>
       </c>
       <c r="G12" t="n">
-        <v>132405</v>
+        <v>89102</v>
+      </c>
+      <c r="H12" t="n">
+        <v>9.591200000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -742,25 +800,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14143</v>
+        <v>17978</v>
       </c>
       <c r="D13" t="n">
-        <v>263207</v>
+        <v>968517</v>
       </c>
       <c r="E13" t="n">
-        <v>5771</v>
+        <v>13991</v>
       </c>
       <c r="F13" t="n">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="G13" t="n">
-        <v>109650</v>
+        <v>88683</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.9329</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -769,25 +830,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17380</v>
+        <v>17713</v>
       </c>
       <c r="D14" t="n">
-        <v>852401</v>
+        <v>322193</v>
       </c>
       <c r="E14" t="n">
-        <v>13894</v>
+        <v>5922</v>
       </c>
       <c r="F14" t="n">
-        <v>216</v>
+        <v>296</v>
       </c>
       <c r="G14" t="n">
-        <v>64152</v>
+        <v>140304</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7.921</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -796,25 +860,28 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15571</v>
+        <v>6592</v>
       </c>
       <c r="D15" t="n">
-        <v>437612</v>
+        <v>105361</v>
       </c>
       <c r="E15" t="n">
-        <v>8207</v>
+        <v>3187</v>
       </c>
       <c r="F15" t="n">
-        <v>274</v>
+        <v>139</v>
       </c>
       <c r="G15" t="n">
-        <v>89324</v>
+        <v>66720</v>
+      </c>
+      <c r="H15" t="n">
+        <v>10.1214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -823,52 +890,58 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6200</v>
+        <v>15052</v>
       </c>
       <c r="D16" t="n">
-        <v>156109</v>
+        <v>233629</v>
       </c>
       <c r="E16" t="n">
-        <v>2207</v>
+        <v>7284</v>
       </c>
       <c r="F16" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G16" t="n">
-        <v>77894</v>
+        <v>78084</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5.1876</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-07-03</t>
+          <t>2024-07-04</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>10158</v>
+        <v>12461</v>
       </c>
       <c r="D17" t="n">
-        <v>386633</v>
+        <v>275679</v>
       </c>
       <c r="E17" t="n">
-        <v>5001</v>
+        <v>4914</v>
       </c>
       <c r="F17" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="G17" t="n">
-        <v>61304</v>
+        <v>59508</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.7755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -877,25 +950,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11205</v>
+        <v>17219</v>
       </c>
       <c r="D18" t="n">
-        <v>262303</v>
+        <v>570237</v>
       </c>
       <c r="E18" t="n">
-        <v>3174</v>
+        <v>10301</v>
       </c>
       <c r="F18" t="n">
-        <v>300</v>
+        <v>268</v>
       </c>
       <c r="G18" t="n">
-        <v>122700</v>
+        <v>68072</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.9533</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -904,25 +980,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14724</v>
+        <v>15732</v>
       </c>
       <c r="D19" t="n">
-        <v>752439</v>
+        <v>401176</v>
       </c>
       <c r="E19" t="n">
-        <v>8759</v>
+        <v>6778</v>
       </c>
       <c r="F19" t="n">
-        <v>219</v>
+        <v>305</v>
       </c>
       <c r="G19" t="n">
-        <v>79716</v>
+        <v>143655</v>
+      </c>
+      <c r="H19" t="n">
+        <v>9.131399999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -931,25 +1010,28 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14846</v>
+        <v>9576</v>
       </c>
       <c r="D20" t="n">
-        <v>512819</v>
+        <v>121100</v>
       </c>
       <c r="E20" t="n">
-        <v>8743</v>
+        <v>3192</v>
       </c>
       <c r="F20" t="n">
-        <v>253</v>
+        <v>161</v>
       </c>
       <c r="G20" t="n">
-        <v>77671</v>
+        <v>85652</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8.9444</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -958,52 +1040,58 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6454</v>
+        <v>13732</v>
       </c>
       <c r="D21" t="n">
-        <v>164635</v>
+        <v>263033</v>
       </c>
       <c r="E21" t="n">
-        <v>2443</v>
+        <v>5776</v>
       </c>
       <c r="F21" t="n">
-        <v>145</v>
+        <v>259</v>
       </c>
       <c r="G21" t="n">
-        <v>61625</v>
+        <v>84175</v>
+      </c>
+      <c r="H21" t="n">
+        <v>6.1298</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-07-04</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15531</v>
+        <v>12965</v>
       </c>
       <c r="D22" t="n">
-        <v>230037</v>
+        <v>213301</v>
       </c>
       <c r="E22" t="n">
-        <v>4247</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="n">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="G22" t="n">
-        <v>110880</v>
+        <v>102408</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.8988</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1012,25 +1100,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>12223</v>
+        <v>15038</v>
       </c>
       <c r="D23" t="n">
-        <v>253869</v>
+        <v>534614</v>
       </c>
       <c r="E23" t="n">
-        <v>3424</v>
+        <v>14330</v>
       </c>
       <c r="F23" t="n">
-        <v>202</v>
+        <v>270</v>
       </c>
       <c r="G23" t="n">
-        <v>63832</v>
+        <v>85050</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.6557</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1039,25 +1130,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>13147</v>
+        <v>17358</v>
       </c>
       <c r="D24" t="n">
-        <v>609034</v>
+        <v>573541</v>
       </c>
       <c r="E24" t="n">
-        <v>12283</v>
+        <v>8706</v>
       </c>
       <c r="F24" t="n">
-        <v>329</v>
+        <v>198</v>
       </c>
       <c r="G24" t="n">
-        <v>88172</v>
+        <v>80784</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.654</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1066,25 +1160,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14601</v>
+        <v>10977</v>
       </c>
       <c r="D25" t="n">
-        <v>584278</v>
+        <v>134185</v>
       </c>
       <c r="E25" t="n">
-        <v>5385</v>
+        <v>3753</v>
       </c>
       <c r="F25" t="n">
-        <v>291</v>
+        <v>155</v>
       </c>
       <c r="G25" t="n">
-        <v>102432</v>
+        <v>63240</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5.7611</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1093,52 +1190,58 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>7127</v>
+        <v>15250</v>
       </c>
       <c r="D26" t="n">
-        <v>197574</v>
+        <v>373238</v>
       </c>
       <c r="E26" t="n">
-        <v>3023</v>
+        <v>5083</v>
       </c>
       <c r="F26" t="n">
-        <v>122</v>
+        <v>182</v>
       </c>
       <c r="G26" t="n">
-        <v>47092</v>
+        <v>85358</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5.5972</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>14458</v>
+        <v>9872</v>
       </c>
       <c r="D27" t="n">
-        <v>384243</v>
+        <v>220447</v>
       </c>
       <c r="E27" t="n">
-        <v>7627</v>
+        <v>4571</v>
       </c>
       <c r="F27" t="n">
-        <v>203</v>
+        <v>279</v>
       </c>
       <c r="G27" t="n">
-        <v>94192</v>
+        <v>101835</v>
+      </c>
+      <c r="H27" t="n">
+        <v>10.3155</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1147,25 +1250,28 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14007</v>
+        <v>17517</v>
       </c>
       <c r="D28" t="n">
-        <v>153014</v>
+        <v>949266</v>
       </c>
       <c r="E28" t="n">
-        <v>4795</v>
+        <v>13410</v>
       </c>
       <c r="F28" t="n">
-        <v>293</v>
+        <v>395</v>
       </c>
       <c r="G28" t="n">
-        <v>116907</v>
+        <v>119685</v>
+      </c>
+      <c r="H28" t="n">
+        <v>6.8325</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1174,25 +1280,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>17779</v>
+        <v>11879</v>
       </c>
       <c r="D29" t="n">
-        <v>700322</v>
+        <v>526158</v>
       </c>
       <c r="E29" t="n">
-        <v>9681</v>
+        <v>6360</v>
       </c>
       <c r="F29" t="n">
-        <v>340</v>
+        <v>188</v>
       </c>
       <c r="G29" t="n">
-        <v>107100</v>
+        <v>63356</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.3334</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1201,25 +1310,28 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>10610</v>
+        <v>8949</v>
       </c>
       <c r="D30" t="n">
-        <v>541010</v>
+        <v>148170</v>
       </c>
       <c r="E30" t="n">
-        <v>8828</v>
+        <v>2201</v>
       </c>
       <c r="F30" t="n">
-        <v>343</v>
+        <v>178</v>
       </c>
       <c r="G30" t="n">
-        <v>164640</v>
+        <v>66750</v>
+      </c>
+      <c r="H30" t="n">
+        <v>7.4589</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1228,52 +1340,58 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>6646</v>
+        <v>8749</v>
       </c>
       <c r="D31" t="n">
-        <v>184415</v>
+        <v>311900</v>
       </c>
       <c r="E31" t="n">
-        <v>2985</v>
+        <v>7855</v>
       </c>
       <c r="F31" t="n">
-        <v>121</v>
+        <v>231</v>
       </c>
       <c r="G31" t="n">
-        <v>51909</v>
+        <v>107415</v>
+      </c>
+      <c r="H31" t="n">
+        <v>12.2774</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-07-07</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>8601</v>
+        <v>14202</v>
       </c>
       <c r="D32" t="n">
-        <v>311699</v>
+        <v>208317</v>
       </c>
       <c r="E32" t="n">
-        <v>7480</v>
+        <v>3056</v>
       </c>
       <c r="F32" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G32" t="n">
-        <v>59786</v>
+        <v>68340</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.812</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1282,25 +1400,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>8052</v>
+        <v>19169</v>
       </c>
       <c r="D33" t="n">
-        <v>290399</v>
+        <v>773557</v>
       </c>
       <c r="E33" t="n">
-        <v>4723</v>
+        <v>8661</v>
       </c>
       <c r="F33" t="n">
-        <v>151</v>
+        <v>238</v>
       </c>
       <c r="G33" t="n">
-        <v>50585</v>
+        <v>68068</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.5509</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1309,25 +1430,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>17962</v>
+        <v>13670</v>
       </c>
       <c r="D34" t="n">
-        <v>907156</v>
+        <v>597723</v>
       </c>
       <c r="E34" t="n">
-        <v>14691</v>
+        <v>6851</v>
       </c>
       <c r="F34" t="n">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="G34" t="n">
-        <v>85215</v>
+        <v>128250</v>
+      </c>
+      <c r="H34" t="n">
+        <v>9.3819</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1336,25 +1460,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>10257</v>
+        <v>8372</v>
       </c>
       <c r="D35" t="n">
-        <v>312726</v>
+        <v>117673</v>
       </c>
       <c r="E35" t="n">
-        <v>9534</v>
+        <v>2407</v>
       </c>
       <c r="F35" t="n">
-        <v>250</v>
+        <v>197</v>
       </c>
       <c r="G35" t="n">
-        <v>92500</v>
+        <v>105789</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12.636</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1363,52 +1490,58 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8028</v>
+        <v>12831</v>
       </c>
       <c r="D36" t="n">
-        <v>151097</v>
+        <v>398420</v>
       </c>
       <c r="E36" t="n">
-        <v>2184</v>
+        <v>7126</v>
       </c>
       <c r="F36" t="n">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="G36" t="n">
-        <v>84108</v>
+        <v>96140</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.4928</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>10409</v>
+        <v>12182</v>
       </c>
       <c r="D37" t="n">
-        <v>365133</v>
+        <v>168221</v>
       </c>
       <c r="E37" t="n">
-        <v>7984</v>
+        <v>3247</v>
       </c>
       <c r="F37" t="n">
-        <v>290</v>
+        <v>223</v>
       </c>
       <c r="G37" t="n">
-        <v>131370</v>
+        <v>84740</v>
+      </c>
+      <c r="H37" t="n">
+        <v>6.9562</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1417,25 +1550,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>14276</v>
+        <v>12781</v>
       </c>
       <c r="D38" t="n">
-        <v>188363</v>
+        <v>625771</v>
       </c>
       <c r="E38" t="n">
-        <v>4961</v>
+        <v>10577</v>
       </c>
       <c r="F38" t="n">
-        <v>278</v>
+        <v>328</v>
       </c>
       <c r="G38" t="n">
-        <v>103416</v>
+        <v>102664</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.032500000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1444,25 +1580,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18338</v>
+        <v>17725</v>
       </c>
       <c r="D39" t="n">
-        <v>650091</v>
+        <v>506029</v>
       </c>
       <c r="E39" t="n">
-        <v>11961</v>
+        <v>7238</v>
       </c>
       <c r="F39" t="n">
-        <v>384</v>
+        <v>280</v>
       </c>
       <c r="G39" t="n">
-        <v>138624</v>
+        <v>96600</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.4499</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1471,25 +1610,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>15574</v>
+        <v>11142</v>
       </c>
       <c r="D40" t="n">
-        <v>363009</v>
+        <v>155777</v>
       </c>
       <c r="E40" t="n">
-        <v>9192</v>
+        <v>2551</v>
       </c>
       <c r="F40" t="n">
-        <v>239</v>
+        <v>194</v>
       </c>
       <c r="G40" t="n">
-        <v>90103</v>
+        <v>77406</v>
+      </c>
+      <c r="H40" t="n">
+        <v>6.9472</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1498,52 +1640,58 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7800</v>
+        <v>15931</v>
       </c>
       <c r="D41" t="n">
-        <v>130481</v>
+        <v>204653</v>
       </c>
       <c r="E41" t="n">
-        <v>2005</v>
+        <v>5936</v>
       </c>
       <c r="F41" t="n">
-        <v>172</v>
+        <v>298</v>
       </c>
       <c r="G41" t="n">
-        <v>66736</v>
+        <v>126948</v>
+      </c>
+      <c r="H41" t="n">
+        <v>7.9686</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-07-08</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>9305</v>
+        <v>14752</v>
       </c>
       <c r="D42" t="n">
-        <v>345719</v>
+        <v>245581</v>
       </c>
       <c r="E42" t="n">
-        <v>5863</v>
+        <v>3908</v>
       </c>
       <c r="F42" t="n">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="G42" t="n">
-        <v>92050</v>
+        <v>64468</v>
+      </c>
+      <c r="H42" t="n">
+        <v>4.3701</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1552,25 +1700,28 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>13912</v>
+        <v>13321</v>
       </c>
       <c r="D43" t="n">
-        <v>203397</v>
+        <v>878397</v>
       </c>
       <c r="E43" t="n">
-        <v>5481</v>
+        <v>8400</v>
       </c>
       <c r="F43" t="n">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="G43" t="n">
-        <v>96900</v>
+        <v>75576</v>
+      </c>
+      <c r="H43" t="n">
+        <v>5.6734</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1579,25 +1730,28 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>13453</v>
+        <v>16661</v>
       </c>
       <c r="D44" t="n">
-        <v>538994</v>
+        <v>353558</v>
       </c>
       <c r="E44" t="n">
-        <v>9479</v>
+        <v>5929</v>
       </c>
       <c r="F44" t="n">
-        <v>243</v>
+        <v>217</v>
       </c>
       <c r="G44" t="n">
-        <v>80676</v>
+        <v>66836</v>
+      </c>
+      <c r="H44" t="n">
+        <v>4.0115</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1606,25 +1760,28 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>10198</v>
+        <v>6949</v>
       </c>
       <c r="D45" t="n">
-        <v>358211</v>
+        <v>173877</v>
       </c>
       <c r="E45" t="n">
-        <v>9672</v>
+        <v>3438</v>
       </c>
       <c r="F45" t="n">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="G45" t="n">
-        <v>70077</v>
+        <v>50858</v>
+      </c>
+      <c r="H45" t="n">
+        <v>7.3188</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1633,52 +1790,58 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>11509</v>
+        <v>13192</v>
       </c>
       <c r="D46" t="n">
-        <v>123591</v>
+        <v>288024</v>
       </c>
       <c r="E46" t="n">
-        <v>2022</v>
+        <v>5016</v>
       </c>
       <c r="F46" t="n">
-        <v>194</v>
+        <v>169</v>
       </c>
       <c r="G46" t="n">
-        <v>89240</v>
+        <v>64051</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4.8553</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>13148</v>
+        <v>12698</v>
       </c>
       <c r="D47" t="n">
-        <v>376652</v>
+        <v>187540</v>
       </c>
       <c r="E47" t="n">
-        <v>5104</v>
+        <v>4607</v>
       </c>
       <c r="F47" t="n">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="G47" t="n">
-        <v>71621</v>
+        <v>79386</v>
+      </c>
+      <c r="H47" t="n">
+        <v>6.2519</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1687,25 +1850,28 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8097</v>
+        <v>14151</v>
       </c>
       <c r="D48" t="n">
-        <v>195722</v>
+        <v>576895</v>
       </c>
       <c r="E48" t="n">
-        <v>3851</v>
+        <v>11402</v>
       </c>
       <c r="F48" t="n">
-        <v>175</v>
+        <v>374</v>
       </c>
       <c r="G48" t="n">
-        <v>60900</v>
+        <v>121924</v>
+      </c>
+      <c r="H48" t="n">
+        <v>8.6159</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1714,25 +1880,28 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>19434</v>
+        <v>10891</v>
       </c>
       <c r="D49" t="n">
-        <v>568480</v>
+        <v>458452</v>
       </c>
       <c r="E49" t="n">
-        <v>8790</v>
+        <v>5196</v>
       </c>
       <c r="F49" t="n">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="G49" t="n">
-        <v>84502</v>
+        <v>107184</v>
+      </c>
+      <c r="H49" t="n">
+        <v>9.8415</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1741,25 +1910,28 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>15964</v>
+        <v>8880</v>
       </c>
       <c r="D50" t="n">
-        <v>458831</v>
+        <v>168348</v>
       </c>
       <c r="E50" t="n">
-        <v>7996</v>
+        <v>2533</v>
       </c>
       <c r="F50" t="n">
-        <v>248</v>
+        <v>147</v>
       </c>
       <c r="G50" t="n">
-        <v>92504</v>
+        <v>62622</v>
+      </c>
+      <c r="H50" t="n">
+        <v>7.052</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1768,52 +1940,58 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>11164</v>
+        <v>14725</v>
       </c>
       <c r="D51" t="n">
-        <v>163720</v>
+        <v>371249</v>
       </c>
       <c r="E51" t="n">
-        <v>3089</v>
+        <v>4295</v>
       </c>
       <c r="F51" t="n">
-        <v>120</v>
+        <v>188</v>
       </c>
       <c r="G51" t="n">
-        <v>42960</v>
+        <v>89676</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6.0901</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>14630</v>
+        <v>14097</v>
       </c>
       <c r="D52" t="n">
-        <v>359112</v>
+        <v>246366</v>
       </c>
       <c r="E52" t="n">
-        <v>6690</v>
+        <v>5109</v>
       </c>
       <c r="F52" t="n">
-        <v>266</v>
+        <v>182</v>
       </c>
       <c r="G52" t="n">
-        <v>101612</v>
+        <v>69706</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.9447</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1822,25 +2000,28 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12587</v>
+        <v>14842</v>
       </c>
       <c r="D53" t="n">
-        <v>217029</v>
+        <v>698654</v>
       </c>
       <c r="E53" t="n">
-        <v>4349</v>
+        <v>8239</v>
       </c>
       <c r="F53" t="n">
-        <v>197</v>
+        <v>382</v>
       </c>
       <c r="G53" t="n">
-        <v>83528</v>
+        <v>142486</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9.600199999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1849,25 +2030,28 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>17173</v>
+        <v>16523</v>
       </c>
       <c r="D54" t="n">
-        <v>828565</v>
+        <v>561500</v>
       </c>
       <c r="E54" t="n">
-        <v>9097</v>
+        <v>5862</v>
       </c>
       <c r="F54" t="n">
-        <v>241</v>
+        <v>324</v>
       </c>
       <c r="G54" t="n">
-        <v>85314</v>
+        <v>132516</v>
+      </c>
+      <c r="H54" t="n">
+        <v>8.020099999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1876,25 +2060,28 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>14122</v>
+        <v>10918</v>
       </c>
       <c r="D55" t="n">
-        <v>541599</v>
+        <v>131725</v>
       </c>
       <c r="E55" t="n">
-        <v>9426</v>
+        <v>3811</v>
       </c>
       <c r="F55" t="n">
-        <v>311</v>
+        <v>144</v>
       </c>
       <c r="G55" t="n">
-        <v>129376</v>
+        <v>61344</v>
+      </c>
+      <c r="H55" t="n">
+        <v>5.6186</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1903,52 +2090,58 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6175</v>
+        <v>12879</v>
       </c>
       <c r="D56" t="n">
-        <v>160100</v>
+        <v>313019</v>
       </c>
       <c r="E56" t="n">
-        <v>2255</v>
+        <v>4597</v>
       </c>
       <c r="F56" t="n">
-        <v>181</v>
+        <v>233</v>
       </c>
       <c r="G56" t="n">
-        <v>67332</v>
+        <v>104151</v>
+      </c>
+      <c r="H56" t="n">
+        <v>8.0869</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8783</v>
+        <v>12152</v>
       </c>
       <c r="D57" t="n">
-        <v>201762</v>
+        <v>232711</v>
       </c>
       <c r="E57" t="n">
-        <v>4514</v>
+        <v>5629</v>
       </c>
       <c r="F57" t="n">
-        <v>197</v>
+        <v>270</v>
       </c>
       <c r="G57" t="n">
-        <v>97121</v>
+        <v>92070</v>
+      </c>
+      <c r="H57" t="n">
+        <v>7.5765</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1957,25 +2150,28 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>14523</v>
+        <v>13991</v>
       </c>
       <c r="D58" t="n">
-        <v>293787</v>
+        <v>549225</v>
       </c>
       <c r="E58" t="n">
-        <v>4717</v>
+        <v>11704</v>
       </c>
       <c r="F58" t="n">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="G58" t="n">
-        <v>121125</v>
+        <v>79704</v>
+      </c>
+      <c r="H58" t="n">
+        <v>5.6968</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1984,25 +2180,28 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13863</v>
+        <v>11178</v>
       </c>
       <c r="D59" t="n">
-        <v>871923</v>
+        <v>375289</v>
       </c>
       <c r="E59" t="n">
-        <v>8188</v>
+        <v>6894</v>
       </c>
       <c r="F59" t="n">
-        <v>241</v>
+        <v>349</v>
       </c>
       <c r="G59" t="n">
-        <v>73505</v>
+        <v>137157</v>
+      </c>
+      <c r="H59" t="n">
+        <v>12.2703</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2011,25 +2210,28 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>17260</v>
+        <v>10905</v>
       </c>
       <c r="D60" t="n">
-        <v>592036</v>
+        <v>144614</v>
       </c>
       <c r="E60" t="n">
-        <v>8253</v>
+        <v>2920</v>
       </c>
       <c r="F60" t="n">
-        <v>318</v>
+        <v>165</v>
       </c>
       <c r="G60" t="n">
-        <v>132924</v>
+        <v>62205</v>
+      </c>
+      <c r="H60" t="n">
+        <v>5.7043</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2038,52 +2240,58 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>9243</v>
+        <v>13645</v>
       </c>
       <c r="D61" t="n">
-        <v>183543</v>
+        <v>329942</v>
       </c>
       <c r="E61" t="n">
-        <v>2674</v>
+        <v>6423</v>
       </c>
       <c r="F61" t="n">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="G61" t="n">
-        <v>74200</v>
+        <v>109975</v>
+      </c>
+      <c r="H61" t="n">
+        <v>8.059699999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-13</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9359</v>
+        <v>13979</v>
       </c>
       <c r="D62" t="n">
-        <v>253638</v>
+        <v>276266</v>
       </c>
       <c r="E62" t="n">
-        <v>7475</v>
+        <v>5224</v>
       </c>
       <c r="F62" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="G62" t="n">
-        <v>64050</v>
+        <v>86520</v>
+      </c>
+      <c r="H62" t="n">
+        <v>6.1893</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2092,25 +2300,28 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>11077</v>
+        <v>18925</v>
       </c>
       <c r="D63" t="n">
-        <v>170005</v>
+        <v>984383</v>
       </c>
       <c r="E63" t="n">
-        <v>5289</v>
+        <v>11186</v>
       </c>
       <c r="F63" t="n">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G63" t="n">
-        <v>80184</v>
+        <v>64232</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.394</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2119,25 +2330,28 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>16424</v>
+        <v>14847</v>
       </c>
       <c r="D64" t="n">
-        <v>651114</v>
+        <v>300399</v>
       </c>
       <c r="E64" t="n">
-        <v>8270</v>
+        <v>9164</v>
       </c>
       <c r="F64" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="G64" t="n">
-        <v>54200</v>
+        <v>107900</v>
+      </c>
+      <c r="H64" t="n">
+        <v>7.2675</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2146,25 +2360,28 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>16218</v>
+        <v>8919</v>
       </c>
       <c r="D65" t="n">
-        <v>488546</v>
+        <v>151889</v>
       </c>
       <c r="E65" t="n">
-        <v>8153</v>
+        <v>2558</v>
       </c>
       <c r="F65" t="n">
-        <v>187</v>
+        <v>122</v>
       </c>
       <c r="G65" t="n">
-        <v>83963</v>
+        <v>47336</v>
+      </c>
+      <c r="H65" t="n">
+        <v>5.3073</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2173,52 +2390,58 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7301</v>
+        <v>13065</v>
       </c>
       <c r="D66" t="n">
-        <v>135704</v>
+        <v>268957</v>
       </c>
       <c r="E66" t="n">
-        <v>3716</v>
+        <v>4748</v>
       </c>
       <c r="F66" t="n">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="G66" t="n">
-        <v>62458</v>
+        <v>84065</v>
+      </c>
+      <c r="H66" t="n">
+        <v>6.4344</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-07-13</t>
+          <t>2024-07-14</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>12512</v>
+        <v>10874</v>
       </c>
       <c r="D67" t="n">
-        <v>314712</v>
+        <v>220202</v>
       </c>
       <c r="E67" t="n">
-        <v>6286</v>
+        <v>5583</v>
       </c>
       <c r="F67" t="n">
-        <v>202</v>
+        <v>254</v>
       </c>
       <c r="G67" t="n">
-        <v>71912</v>
+        <v>114046</v>
+      </c>
+      <c r="H67" t="n">
+        <v>10.488</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2227,25 +2450,28 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>12458</v>
+        <v>12622</v>
       </c>
       <c r="D68" t="n">
-        <v>273765</v>
+        <v>670388</v>
       </c>
       <c r="E68" t="n">
-        <v>3301</v>
+        <v>14662</v>
       </c>
       <c r="F68" t="n">
-        <v>262</v>
+        <v>225</v>
       </c>
       <c r="G68" t="n">
-        <v>94320</v>
+        <v>76500</v>
+      </c>
+      <c r="H68" t="n">
+        <v>6.0608</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2254,25 +2480,28 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>12715</v>
+        <v>14416</v>
       </c>
       <c r="D69" t="n">
-        <v>572830</v>
+        <v>386490</v>
       </c>
       <c r="E69" t="n">
-        <v>11863</v>
+        <v>5334</v>
       </c>
       <c r="F69" t="n">
-        <v>355</v>
+        <v>255</v>
       </c>
       <c r="G69" t="n">
-        <v>90880</v>
+        <v>109395</v>
+      </c>
+      <c r="H69" t="n">
+        <v>7.5884</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2281,25 +2510,28 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>15148</v>
+        <v>10896</v>
       </c>
       <c r="D70" t="n">
-        <v>365181</v>
+        <v>150361</v>
       </c>
       <c r="E70" t="n">
-        <v>6112</v>
+        <v>2019</v>
       </c>
       <c r="F70" t="n">
-        <v>318</v>
+        <v>126</v>
       </c>
       <c r="G70" t="n">
-        <v>114480</v>
+        <v>65898</v>
+      </c>
+      <c r="H70" t="n">
+        <v>6.0479</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2308,52 +2540,58 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7567</v>
+        <v>14143</v>
       </c>
       <c r="D71" t="n">
-        <v>124529</v>
+        <v>380655</v>
       </c>
       <c r="E71" t="n">
-        <v>3649</v>
+        <v>4178</v>
       </c>
       <c r="F71" t="n">
-        <v>187</v>
+        <v>268</v>
       </c>
       <c r="G71" t="n">
-        <v>96118</v>
+        <v>129176</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9.133599999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2024-07-15</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>10826</v>
+        <v>10259</v>
       </c>
       <c r="D72" t="n">
-        <v>256041</v>
+        <v>283653</v>
       </c>
       <c r="E72" t="n">
-        <v>4114</v>
+        <v>4753</v>
       </c>
       <c r="F72" t="n">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="G72" t="n">
-        <v>110625</v>
+        <v>92276</v>
+      </c>
+      <c r="H72" t="n">
+        <v>8.9946</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2362,25 +2600,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>12408</v>
+        <v>16046</v>
       </c>
       <c r="D73" t="n">
-        <v>184387</v>
+        <v>679425</v>
       </c>
       <c r="E73" t="n">
-        <v>3836</v>
+        <v>14690</v>
       </c>
       <c r="F73" t="n">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="G73" t="n">
-        <v>85377</v>
+        <v>76362</v>
+      </c>
+      <c r="H73" t="n">
+        <v>4.7589</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2389,25 +2630,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>18139</v>
+        <v>17341</v>
       </c>
       <c r="D74" t="n">
-        <v>576966</v>
+        <v>321012</v>
       </c>
       <c r="E74" t="n">
-        <v>11748</v>
+        <v>8635</v>
       </c>
       <c r="F74" t="n">
-        <v>294</v>
+        <v>235</v>
       </c>
       <c r="G74" t="n">
-        <v>95844</v>
+        <v>82955</v>
+      </c>
+      <c r="H74" t="n">
+        <v>4.7837</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2416,25 +2660,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>16321</v>
+        <v>10570</v>
       </c>
       <c r="D75" t="n">
-        <v>399362</v>
+        <v>161384</v>
       </c>
       <c r="E75" t="n">
-        <v>9117</v>
+        <v>3982</v>
       </c>
       <c r="F75" t="n">
-        <v>285</v>
+        <v>140</v>
       </c>
       <c r="G75" t="n">
-        <v>117420</v>
+        <v>61460</v>
+      </c>
+      <c r="H75" t="n">
+        <v>5.8146</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2443,52 +2690,58 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>7193</v>
+        <v>15377</v>
       </c>
       <c r="D76" t="n">
-        <v>125265</v>
+        <v>295301</v>
       </c>
       <c r="E76" t="n">
-        <v>3332</v>
+        <v>5999</v>
       </c>
       <c r="F76" t="n">
-        <v>186</v>
+        <v>271</v>
       </c>
       <c r="G76" t="n">
-        <v>79980</v>
+        <v>96747</v>
+      </c>
+      <c r="H76" t="n">
+        <v>6.2917</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-07-15</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>12349</v>
+        <v>13768</v>
       </c>
       <c r="D77" t="n">
-        <v>302716</v>
+        <v>150193</v>
       </c>
       <c r="E77" t="n">
-        <v>4347</v>
+        <v>4747</v>
       </c>
       <c r="F77" t="n">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="G77" t="n">
-        <v>102821</v>
+        <v>102621</v>
+      </c>
+      <c r="H77" t="n">
+        <v>7.4536</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2497,25 +2750,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>10610</v>
+        <v>15188</v>
       </c>
       <c r="D78" t="n">
-        <v>153626</v>
+        <v>518835</v>
       </c>
       <c r="E78" t="n">
-        <v>5569</v>
+        <v>9061</v>
       </c>
       <c r="F78" t="n">
-        <v>216</v>
+        <v>396</v>
       </c>
       <c r="G78" t="n">
-        <v>84672</v>
+        <v>103356</v>
+      </c>
+      <c r="H78" t="n">
+        <v>6.8051</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2524,25 +2780,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>13393</v>
+        <v>17947</v>
       </c>
       <c r="D79" t="n">
-        <v>655527</v>
+        <v>538409</v>
       </c>
       <c r="E79" t="n">
-        <v>11737</v>
+        <v>8657</v>
       </c>
       <c r="F79" t="n">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="G79" t="n">
-        <v>97146</v>
+        <v>91168</v>
+      </c>
+      <c r="H79" t="n">
+        <v>5.0798</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2551,25 +2810,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>13013</v>
+        <v>9796</v>
       </c>
       <c r="D80" t="n">
-        <v>460214</v>
+        <v>116513</v>
       </c>
       <c r="E80" t="n">
-        <v>9048</v>
+        <v>3806</v>
       </c>
       <c r="F80" t="n">
-        <v>271</v>
+        <v>112</v>
       </c>
       <c r="G80" t="n">
-        <v>103793</v>
+        <v>52080</v>
+      </c>
+      <c r="H80" t="n">
+        <v>5.3165</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2578,52 +2840,58 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9578</v>
+        <v>12780</v>
       </c>
       <c r="D81" t="n">
-        <v>142292</v>
+        <v>266142</v>
       </c>
       <c r="E81" t="n">
-        <v>3870</v>
+        <v>4297</v>
       </c>
       <c r="F81" t="n">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="G81" t="n">
-        <v>88677</v>
+        <v>124483</v>
+      </c>
+      <c r="H81" t="n">
+        <v>9.740500000000001</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>11464</v>
+        <v>11429</v>
       </c>
       <c r="D82" t="n">
-        <v>221878</v>
+        <v>270053</v>
       </c>
       <c r="E82" t="n">
-        <v>5922</v>
+        <v>4881</v>
       </c>
       <c r="F82" t="n">
-        <v>242</v>
+        <v>299</v>
       </c>
       <c r="G82" t="n">
-        <v>92928</v>
+        <v>128570</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11.2495</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2632,25 +2900,28 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>14421</v>
+        <v>16240</v>
       </c>
       <c r="D83" t="n">
-        <v>225326</v>
+        <v>552505</v>
       </c>
       <c r="E83" t="n">
-        <v>3233</v>
+        <v>12239</v>
       </c>
       <c r="F83" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G83" t="n">
-        <v>91540</v>
+        <v>63054</v>
+      </c>
+      <c r="H83" t="n">
+        <v>3.8826</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2659,25 +2930,28 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>12697</v>
+        <v>11971</v>
       </c>
       <c r="D84" t="n">
-        <v>895311</v>
+        <v>382887</v>
       </c>
       <c r="E84" t="n">
-        <v>9866</v>
+        <v>5152</v>
       </c>
       <c r="F84" t="n">
-        <v>390</v>
+        <v>274</v>
       </c>
       <c r="G84" t="n">
-        <v>112320</v>
+        <v>121930</v>
+      </c>
+      <c r="H84" t="n">
+        <v>10.1854</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2686,25 +2960,28 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>12371</v>
+        <v>7492</v>
       </c>
       <c r="D85" t="n">
-        <v>387446</v>
+        <v>188727</v>
       </c>
       <c r="E85" t="n">
-        <v>9176</v>
+        <v>2412</v>
       </c>
       <c r="F85" t="n">
-        <v>234</v>
+        <v>166</v>
       </c>
       <c r="G85" t="n">
-        <v>86112</v>
+        <v>78186</v>
+      </c>
+      <c r="H85" t="n">
+        <v>10.4359</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2713,52 +2990,58 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8689</v>
+        <v>8916</v>
       </c>
       <c r="D86" t="n">
-        <v>100530</v>
+        <v>357411</v>
       </c>
       <c r="E86" t="n">
-        <v>2233</v>
+        <v>6043</v>
       </c>
       <c r="F86" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G86" t="n">
-        <v>63990</v>
+        <v>74909</v>
+      </c>
+      <c r="H86" t="n">
+        <v>8.4016</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>14443</v>
+        <v>14594</v>
       </c>
       <c r="D87" t="n">
-        <v>277656</v>
+        <v>230408</v>
       </c>
       <c r="E87" t="n">
-        <v>7931</v>
+        <v>4783</v>
       </c>
       <c r="F87" t="n">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G87" t="n">
-        <v>103518</v>
+        <v>89856</v>
+      </c>
+      <c r="H87" t="n">
+        <v>6.1571</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2767,25 +3050,28 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>8907</v>
+        <v>12155</v>
       </c>
       <c r="D88" t="n">
-        <v>288762</v>
+        <v>880331</v>
       </c>
       <c r="E88" t="n">
-        <v>5648</v>
+        <v>9748</v>
       </c>
       <c r="F88" t="n">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="G88" t="n">
-        <v>60200</v>
+        <v>131600</v>
+      </c>
+      <c r="H88" t="n">
+        <v>10.8268</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2794,25 +3080,28 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>18439</v>
+        <v>14104</v>
       </c>
       <c r="D89" t="n">
-        <v>719297</v>
+        <v>453102</v>
       </c>
       <c r="E89" t="n">
-        <v>12203</v>
+        <v>8481</v>
       </c>
       <c r="F89" t="n">
-        <v>306</v>
+        <v>340</v>
       </c>
       <c r="G89" t="n">
-        <v>80478</v>
+        <v>105740</v>
+      </c>
+      <c r="H89" t="n">
+        <v>7.4972</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2821,25 +3110,28 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>17849</v>
+        <v>9632</v>
       </c>
       <c r="D90" t="n">
-        <v>569805</v>
+        <v>100943</v>
       </c>
       <c r="E90" t="n">
-        <v>7101</v>
+        <v>3680</v>
       </c>
       <c r="F90" t="n">
-        <v>348</v>
+        <v>125</v>
       </c>
       <c r="G90" t="n">
-        <v>104400</v>
+        <v>52625</v>
+      </c>
+      <c r="H90" t="n">
+        <v>5.4636</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2848,52 +3140,58 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9788</v>
+        <v>9303</v>
       </c>
       <c r="D91" t="n">
-        <v>124040</v>
+        <v>232315</v>
       </c>
       <c r="E91" t="n">
-        <v>2664</v>
+        <v>7192</v>
       </c>
       <c r="F91" t="n">
-        <v>114</v>
+        <v>292</v>
       </c>
       <c r="G91" t="n">
-        <v>50730</v>
+        <v>141620</v>
+      </c>
+      <c r="H91" t="n">
+        <v>15.223</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10756</v>
+        <v>10873</v>
       </c>
       <c r="D92" t="n">
-        <v>293582</v>
+        <v>299537</v>
       </c>
       <c r="E92" t="n">
-        <v>6366</v>
+        <v>4004</v>
       </c>
       <c r="F92" t="n">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="G92" t="n">
-        <v>73470</v>
+        <v>91000</v>
+      </c>
+      <c r="H92" t="n">
+        <v>8.369400000000001</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2902,25 +3200,28 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>11748</v>
+        <v>19457</v>
       </c>
       <c r="D93" t="n">
-        <v>178436</v>
+        <v>575472</v>
       </c>
       <c r="E93" t="n">
-        <v>4068</v>
+        <v>13082</v>
       </c>
       <c r="F93" t="n">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="G93" t="n">
-        <v>97720</v>
+        <v>77056</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3.9603</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2929,25 +3230,28 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>15315</v>
+        <v>15927</v>
       </c>
       <c r="D94" t="n">
-        <v>976715</v>
+        <v>379204</v>
       </c>
       <c r="E94" t="n">
-        <v>13428</v>
+        <v>5823</v>
       </c>
       <c r="F94" t="n">
-        <v>246</v>
+        <v>324</v>
       </c>
       <c r="G94" t="n">
-        <v>67650</v>
+        <v>151308</v>
+      </c>
+      <c r="H94" t="n">
+        <v>9.5001</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2956,25 +3260,28 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>12602</v>
+        <v>6824</v>
       </c>
       <c r="D95" t="n">
-        <v>415272</v>
+        <v>146988</v>
       </c>
       <c r="E95" t="n">
-        <v>7800</v>
+        <v>3520</v>
       </c>
       <c r="F95" t="n">
-        <v>314</v>
+        <v>158</v>
       </c>
       <c r="G95" t="n">
-        <v>145068</v>
+        <v>85636</v>
+      </c>
+      <c r="H95" t="n">
+        <v>12.5492</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2983,52 +3290,58 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>7764</v>
+        <v>11574</v>
       </c>
       <c r="D96" t="n">
-        <v>165105</v>
+        <v>356390</v>
       </c>
       <c r="E96" t="n">
-        <v>2456</v>
+        <v>6853</v>
       </c>
       <c r="F96" t="n">
-        <v>178</v>
+        <v>275</v>
       </c>
       <c r="G96" t="n">
-        <v>95586</v>
+        <v>105875</v>
+      </c>
+      <c r="H96" t="n">
+        <v>9.1477</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-07-20</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>15577</v>
+        <v>14006</v>
       </c>
       <c r="D97" t="n">
-        <v>273994</v>
+        <v>246237</v>
       </c>
       <c r="E97" t="n">
-        <v>6224</v>
+        <v>4392</v>
       </c>
       <c r="F97" t="n">
-        <v>199</v>
+        <v>164</v>
       </c>
       <c r="G97" t="n">
-        <v>83978</v>
+        <v>47068</v>
+      </c>
+      <c r="H97" t="n">
+        <v>3.3606</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3037,25 +3350,28 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>13522</v>
+        <v>13307</v>
       </c>
       <c r="D98" t="n">
-        <v>176580</v>
+        <v>600308</v>
       </c>
       <c r="E98" t="n">
-        <v>3495</v>
+        <v>11235</v>
       </c>
       <c r="F98" t="n">
-        <v>240</v>
+        <v>363</v>
       </c>
       <c r="G98" t="n">
-        <v>84000</v>
+        <v>110715</v>
+      </c>
+      <c r="H98" t="n">
+        <v>8.3201</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3064,25 +3380,28 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>12919</v>
+        <v>12648</v>
       </c>
       <c r="D99" t="n">
-        <v>855113</v>
+        <v>317263</v>
       </c>
       <c r="E99" t="n">
-        <v>11190</v>
+        <v>9682</v>
       </c>
       <c r="F99" t="n">
-        <v>266</v>
+        <v>343</v>
       </c>
       <c r="G99" t="n">
-        <v>98952</v>
+        <v>103586</v>
+      </c>
+      <c r="H99" t="n">
+        <v>8.1899</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3091,25 +3410,28 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>17642</v>
+        <v>6759</v>
       </c>
       <c r="D100" t="n">
-        <v>430212</v>
+        <v>142863</v>
       </c>
       <c r="E100" t="n">
-        <v>8661</v>
+        <v>3319</v>
       </c>
       <c r="F100" t="n">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="G100" t="n">
-        <v>69978</v>
+        <v>43680</v>
+      </c>
+      <c r="H100" t="n">
+        <v>6.4625</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3118,52 +3440,58 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>11491</v>
+        <v>13490</v>
       </c>
       <c r="D101" t="n">
-        <v>125909</v>
+        <v>207257</v>
       </c>
       <c r="E101" t="n">
-        <v>2712</v>
+        <v>6229</v>
       </c>
       <c r="F101" t="n">
-        <v>100</v>
+        <v>157</v>
       </c>
       <c r="G101" t="n">
-        <v>47600</v>
+        <v>54165</v>
+      </c>
+      <c r="H101" t="n">
+        <v>4.0152</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-07-20</t>
+          <t>2024-07-21</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>14861</v>
+        <v>12933</v>
       </c>
       <c r="D102" t="n">
-        <v>326668</v>
+        <v>188658</v>
       </c>
       <c r="E102" t="n">
-        <v>4104</v>
+        <v>4142</v>
       </c>
       <c r="F102" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="G102" t="n">
-        <v>98928</v>
+        <v>79116</v>
+      </c>
+      <c r="H102" t="n">
+        <v>6.1174</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3172,25 +3500,28 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>8503</v>
+        <v>19052</v>
       </c>
       <c r="D103" t="n">
-        <v>177202</v>
+        <v>932147</v>
       </c>
       <c r="E103" t="n">
-        <v>4163</v>
+        <v>10372</v>
       </c>
       <c r="F103" t="n">
-        <v>172</v>
+        <v>397</v>
       </c>
       <c r="G103" t="n">
-        <v>62608</v>
+        <v>105205</v>
+      </c>
+      <c r="H103" t="n">
+        <v>5.522</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3199,25 +3530,28 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>18331</v>
+        <v>17413</v>
       </c>
       <c r="D104" t="n">
-        <v>828600</v>
+        <v>326638</v>
       </c>
       <c r="E104" t="n">
-        <v>8996</v>
+        <v>6922</v>
       </c>
       <c r="F104" t="n">
-        <v>331</v>
+        <v>202</v>
       </c>
       <c r="G104" t="n">
-        <v>115188</v>
+        <v>67468</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3.8746</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3226,25 +3560,28 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>13281</v>
+        <v>11493</v>
       </c>
       <c r="D105" t="n">
-        <v>482381</v>
+        <v>104890</v>
       </c>
       <c r="E105" t="n">
-        <v>9515</v>
+        <v>2933</v>
       </c>
       <c r="F105" t="n">
-        <v>318</v>
+        <v>167</v>
       </c>
       <c r="G105" t="n">
-        <v>141192</v>
+        <v>85170</v>
+      </c>
+      <c r="H105" t="n">
+        <v>7.4106</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3253,52 +3590,58 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>9454</v>
+        <v>8550</v>
       </c>
       <c r="D106" t="n">
-        <v>129574</v>
+        <v>340697</v>
       </c>
       <c r="E106" t="n">
-        <v>2240</v>
+        <v>7103</v>
       </c>
       <c r="F106" t="n">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="G106" t="n">
-        <v>55042</v>
+        <v>104276</v>
+      </c>
+      <c r="H106" t="n">
+        <v>12.196</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-07-21</t>
+          <t>2024-07-22</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>9666</v>
+        <v>13420</v>
       </c>
       <c r="D107" t="n">
-        <v>367294</v>
+        <v>194345</v>
       </c>
       <c r="E107" t="n">
-        <v>6304</v>
+        <v>5857</v>
       </c>
       <c r="F107" t="n">
-        <v>167</v>
+        <v>239</v>
       </c>
       <c r="G107" t="n">
-        <v>67134</v>
+        <v>102292</v>
+      </c>
+      <c r="H107" t="n">
+        <v>7.6224</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3307,25 +3650,28 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11200</v>
+        <v>14752</v>
       </c>
       <c r="D108" t="n">
-        <v>190167</v>
+        <v>586620</v>
       </c>
       <c r="E108" t="n">
-        <v>5387</v>
+        <v>11925</v>
       </c>
       <c r="F108" t="n">
-        <v>224</v>
+        <v>246</v>
       </c>
       <c r="G108" t="n">
-        <v>87360</v>
+        <v>93480</v>
+      </c>
+      <c r="H108" t="n">
+        <v>6.3368</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3334,25 +3680,28 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>14217</v>
+        <v>15042</v>
       </c>
       <c r="D109" t="n">
-        <v>713332</v>
+        <v>406336</v>
       </c>
       <c r="E109" t="n">
-        <v>9244</v>
+        <v>8337</v>
       </c>
       <c r="F109" t="n">
-        <v>279</v>
+        <v>206</v>
       </c>
       <c r="G109" t="n">
-        <v>99045</v>
+        <v>78486</v>
+      </c>
+      <c r="H109" t="n">
+        <v>5.2178</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3361,25 +3710,28 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11524</v>
+        <v>8256</v>
       </c>
       <c r="D110" t="n">
-        <v>585556</v>
+        <v>134684</v>
       </c>
       <c r="E110" t="n">
-        <v>5941</v>
+        <v>2321</v>
       </c>
       <c r="F110" t="n">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="G110" t="n">
-        <v>85568</v>
+        <v>51744</v>
+      </c>
+      <c r="H110" t="n">
+        <v>6.2674</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3388,52 +3740,58 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>6795</v>
+        <v>8751</v>
       </c>
       <c r="D111" t="n">
-        <v>139356</v>
+        <v>254381</v>
       </c>
       <c r="E111" t="n">
-        <v>2943</v>
+        <v>6556</v>
       </c>
       <c r="F111" t="n">
-        <v>147</v>
+        <v>178</v>
       </c>
       <c r="G111" t="n">
-        <v>72177</v>
+        <v>63724</v>
+      </c>
+      <c r="H111" t="n">
+        <v>7.2819</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-07-22</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>15923</v>
+        <v>11857</v>
       </c>
       <c r="D112" t="n">
-        <v>392583</v>
+        <v>185354</v>
       </c>
       <c r="E112" t="n">
-        <v>5473</v>
+        <v>4379</v>
       </c>
       <c r="F112" t="n">
-        <v>285</v>
+        <v>155</v>
       </c>
       <c r="G112" t="n">
-        <v>112860</v>
+        <v>56885</v>
+      </c>
+      <c r="H112" t="n">
+        <v>4.7976</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3442,25 +3800,28 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>11311</v>
+        <v>18921</v>
       </c>
       <c r="D113" t="n">
-        <v>228638</v>
+        <v>890237</v>
       </c>
       <c r="E113" t="n">
-        <v>3534</v>
+        <v>14595</v>
       </c>
       <c r="F113" t="n">
-        <v>189</v>
+        <v>350</v>
       </c>
       <c r="G113" t="n">
-        <v>72009</v>
+        <v>127050</v>
+      </c>
+      <c r="H113" t="n">
+        <v>6.7148</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3469,25 +3830,28 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>19794</v>
+        <v>13423</v>
       </c>
       <c r="D114" t="n">
-        <v>609909</v>
+        <v>393736</v>
       </c>
       <c r="E114" t="n">
-        <v>11465</v>
+        <v>9658</v>
       </c>
       <c r="F114" t="n">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="G114" t="n">
-        <v>97614</v>
+        <v>112230</v>
+      </c>
+      <c r="H114" t="n">
+        <v>8.361000000000001</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3496,25 +3860,28 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>13464</v>
+        <v>10054</v>
       </c>
       <c r="D115" t="n">
-        <v>474350</v>
+        <v>101858</v>
       </c>
       <c r="E115" t="n">
-        <v>5092</v>
+        <v>3431</v>
       </c>
       <c r="F115" t="n">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="G115" t="n">
-        <v>101024</v>
+        <v>64896</v>
+      </c>
+      <c r="H115" t="n">
+        <v>6.4547</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3523,52 +3890,58 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>6518</v>
+        <v>12499</v>
       </c>
       <c r="D116" t="n">
-        <v>141233</v>
+        <v>249339</v>
       </c>
       <c r="E116" t="n">
-        <v>3985</v>
+        <v>4824</v>
       </c>
       <c r="F116" t="n">
-        <v>154</v>
+        <v>223</v>
       </c>
       <c r="G116" t="n">
-        <v>66374</v>
+        <v>103249</v>
+      </c>
+      <c r="H116" t="n">
+        <v>8.2606</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-07-24</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>9728</v>
+        <v>13994</v>
       </c>
       <c r="D117" t="n">
-        <v>302239</v>
+        <v>216789</v>
       </c>
       <c r="E117" t="n">
-        <v>6725</v>
+        <v>3099</v>
       </c>
       <c r="F117" t="n">
-        <v>288</v>
+        <v>256</v>
       </c>
       <c r="G117" t="n">
-        <v>96192</v>
+        <v>92416</v>
+      </c>
+      <c r="H117" t="n">
+        <v>6.604</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3577,25 +3950,28 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>14415</v>
+        <v>17963</v>
       </c>
       <c r="D118" t="n">
-        <v>265471</v>
+        <v>788759</v>
       </c>
       <c r="E118" t="n">
-        <v>4790</v>
+        <v>14579</v>
       </c>
       <c r="F118" t="n">
-        <v>211</v>
+        <v>353</v>
       </c>
       <c r="G118" t="n">
-        <v>79125</v>
+        <v>98487</v>
+      </c>
+      <c r="H118" t="n">
+        <v>5.4828</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3604,25 +3980,28 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>19414</v>
+        <v>15311</v>
       </c>
       <c r="D119" t="n">
-        <v>866737</v>
+        <v>422960</v>
       </c>
       <c r="E119" t="n">
-        <v>13814</v>
+        <v>9378</v>
       </c>
       <c r="F119" t="n">
-        <v>346</v>
+        <v>276</v>
       </c>
       <c r="G119" t="n">
-        <v>126636</v>
+        <v>118956</v>
+      </c>
+      <c r="H119" t="n">
+        <v>7.7693</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3631,25 +4010,28 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>15998</v>
+        <v>6715</v>
       </c>
       <c r="D120" t="n">
-        <v>383154</v>
+        <v>160079</v>
       </c>
       <c r="E120" t="n">
-        <v>7316</v>
+        <v>3990</v>
       </c>
       <c r="F120" t="n">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="G120" t="n">
-        <v>68343</v>
+        <v>71832</v>
+      </c>
+      <c r="H120" t="n">
+        <v>10.6972</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3658,52 +4040,58 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>11078</v>
+        <v>13099</v>
       </c>
       <c r="D121" t="n">
-        <v>180279</v>
+        <v>366441</v>
       </c>
       <c r="E121" t="n">
-        <v>2899</v>
+        <v>7745</v>
       </c>
       <c r="F121" t="n">
-        <v>163</v>
+        <v>298</v>
       </c>
       <c r="G121" t="n">
-        <v>67645</v>
+        <v>96552</v>
+      </c>
+      <c r="H121" t="n">
+        <v>7.3709</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-07-24</t>
+          <t>2024-07-25</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>15281</v>
+        <v>10112</v>
       </c>
       <c r="D122" t="n">
-        <v>224105</v>
+        <v>219901</v>
       </c>
       <c r="E122" t="n">
-        <v>7830</v>
+        <v>4869</v>
       </c>
       <c r="F122" t="n">
-        <v>198</v>
+        <v>150</v>
       </c>
       <c r="G122" t="n">
-        <v>71874</v>
+        <v>58800</v>
+      </c>
+      <c r="H122" t="n">
+        <v>5.8149</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3712,25 +4100,28 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>9067</v>
+        <v>16577</v>
       </c>
       <c r="D123" t="n">
-        <v>286052</v>
+        <v>903132</v>
       </c>
       <c r="E123" t="n">
-        <v>5993</v>
+        <v>11586</v>
       </c>
       <c r="F123" t="n">
-        <v>249</v>
+        <v>328</v>
       </c>
       <c r="G123" t="n">
-        <v>112050</v>
+        <v>114472</v>
+      </c>
+      <c r="H123" t="n">
+        <v>6.9055</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3739,25 +4130,28 @@
         </is>
       </c>
       <c r="C124" t="n">
-        <v>13867</v>
+        <v>16171</v>
       </c>
       <c r="D124" t="n">
-        <v>508278</v>
+        <v>344071</v>
       </c>
       <c r="E124" t="n">
-        <v>11124</v>
+        <v>5638</v>
       </c>
       <c r="F124" t="n">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="G124" t="n">
-        <v>67554</v>
+        <v>123840</v>
+      </c>
+      <c r="H124" t="n">
+        <v>7.6582</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3766,25 +4160,28 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>12495</v>
+        <v>6945</v>
       </c>
       <c r="D125" t="n">
-        <v>327415</v>
+        <v>142228</v>
       </c>
       <c r="E125" t="n">
-        <v>8517</v>
+        <v>2231</v>
       </c>
       <c r="F125" t="n">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="G125" t="n">
-        <v>89505</v>
+        <v>61280</v>
+      </c>
+      <c r="H125" t="n">
+        <v>8.823600000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3793,52 +4190,58 @@
         </is>
       </c>
       <c r="C126" t="n">
-        <v>8818</v>
+        <v>11505</v>
       </c>
       <c r="D126" t="n">
-        <v>109757</v>
+        <v>325456</v>
       </c>
       <c r="E126" t="n">
-        <v>3405</v>
+        <v>4417</v>
       </c>
       <c r="F126" t="n">
-        <v>184</v>
+        <v>242</v>
       </c>
       <c r="G126" t="n">
-        <v>77464</v>
+        <v>93412</v>
+      </c>
+      <c r="H126" t="n">
+        <v>8.119300000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>10651</v>
+        <v>14305</v>
       </c>
       <c r="D127" t="n">
-        <v>235702</v>
+        <v>192620</v>
       </c>
       <c r="E127" t="n">
-        <v>4215</v>
+        <v>3859</v>
       </c>
       <c r="F127" t="n">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="G127" t="n">
-        <v>99060</v>
+        <v>78521</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5.4891</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3847,25 +4250,28 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>12657</v>
+        <v>13203</v>
       </c>
       <c r="D128" t="n">
-        <v>256562</v>
+        <v>671396</v>
       </c>
       <c r="E128" t="n">
-        <v>5568</v>
+        <v>12279</v>
       </c>
       <c r="F128" t="n">
-        <v>222</v>
+        <v>371</v>
       </c>
       <c r="G128" t="n">
-        <v>64824</v>
+        <v>127253</v>
+      </c>
+      <c r="H128" t="n">
+        <v>9.638199999999999</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3874,25 +4280,28 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>19253</v>
+        <v>16721</v>
       </c>
       <c r="D129" t="n">
-        <v>858862</v>
+        <v>343732</v>
       </c>
       <c r="E129" t="n">
-        <v>10023</v>
+        <v>7963</v>
       </c>
       <c r="F129" t="n">
-        <v>381</v>
+        <v>299</v>
       </c>
       <c r="G129" t="n">
-        <v>129159</v>
+        <v>95979</v>
+      </c>
+      <c r="H129" t="n">
+        <v>5.74</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3901,25 +4310,28 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>13862</v>
+        <v>9076</v>
       </c>
       <c r="D130" t="n">
-        <v>372702</v>
+        <v>109920</v>
       </c>
       <c r="E130" t="n">
-        <v>7285</v>
+        <v>3090</v>
       </c>
       <c r="F130" t="n">
-        <v>320</v>
+        <v>135</v>
       </c>
       <c r="G130" t="n">
-        <v>149440</v>
+        <v>52785</v>
+      </c>
+      <c r="H130" t="n">
+        <v>5.8159</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3928,52 +4340,58 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>10451</v>
+        <v>14256</v>
       </c>
       <c r="D131" t="n">
-        <v>175323</v>
+        <v>264404</v>
       </c>
       <c r="E131" t="n">
-        <v>2867</v>
+        <v>5756</v>
       </c>
       <c r="F131" t="n">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G131" t="n">
-        <v>87714</v>
+        <v>72980</v>
+      </c>
+      <c r="H131" t="n">
+        <v>5.1192</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-07-26</t>
+          <t>2024-07-27</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>10316</v>
+        <v>10417</v>
       </c>
       <c r="D132" t="n">
-        <v>267224</v>
+        <v>289656</v>
       </c>
       <c r="E132" t="n">
-        <v>4069</v>
+        <v>5609</v>
       </c>
       <c r="F132" t="n">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="G132" t="n">
-        <v>96074</v>
+        <v>88400</v>
+      </c>
+      <c r="H132" t="n">
+        <v>8.4861</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3982,25 +4400,28 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>11413</v>
+        <v>13324</v>
       </c>
       <c r="D133" t="n">
-        <v>188166</v>
+        <v>732082</v>
       </c>
       <c r="E133" t="n">
-        <v>3738</v>
+        <v>10923</v>
       </c>
       <c r="F133" t="n">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="G133" t="n">
-        <v>68544</v>
+        <v>92411</v>
+      </c>
+      <c r="H133" t="n">
+        <v>6.9357</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4009,25 +4430,28 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>14334</v>
+        <v>15444</v>
       </c>
       <c r="D134" t="n">
-        <v>972659</v>
+        <v>493664</v>
       </c>
       <c r="E134" t="n">
-        <v>8756</v>
+        <v>8083</v>
       </c>
       <c r="F134" t="n">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G134" t="n">
-        <v>103950</v>
+        <v>95665</v>
+      </c>
+      <c r="H134" t="n">
+        <v>6.1943</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4036,25 +4460,28 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>12777</v>
+        <v>10126</v>
       </c>
       <c r="D135" t="n">
-        <v>572601</v>
+        <v>117198</v>
       </c>
       <c r="E135" t="n">
-        <v>5417</v>
+        <v>2586</v>
       </c>
       <c r="F135" t="n">
-        <v>292</v>
+        <v>127</v>
       </c>
       <c r="G135" t="n">
-        <v>88768</v>
+        <v>53213</v>
+      </c>
+      <c r="H135" t="n">
+        <v>5.2551</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4063,52 +4490,58 @@
         </is>
       </c>
       <c r="C136" t="n">
-        <v>7224</v>
+        <v>11629</v>
       </c>
       <c r="D136" t="n">
-        <v>184304</v>
+        <v>255459</v>
       </c>
       <c r="E136" t="n">
-        <v>2130</v>
+        <v>4902</v>
       </c>
       <c r="F136" t="n">
-        <v>103</v>
+        <v>229</v>
       </c>
       <c r="G136" t="n">
-        <v>43260</v>
+        <v>84959</v>
+      </c>
+      <c r="H136" t="n">
+        <v>7.3058</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
+          <t>2024-07-28</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>11290</v>
+        <v>10871</v>
       </c>
       <c r="D137" t="n">
-        <v>227071</v>
+        <v>269148</v>
       </c>
       <c r="E137" t="n">
-        <v>4952</v>
+        <v>3704</v>
       </c>
       <c r="F137" t="n">
-        <v>298</v>
+        <v>221</v>
       </c>
       <c r="G137" t="n">
-        <v>143636</v>
+        <v>95914</v>
+      </c>
+      <c r="H137" t="n">
+        <v>8.822900000000001</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4117,25 +4550,28 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>8195</v>
+        <v>19830</v>
       </c>
       <c r="D138" t="n">
-        <v>268215</v>
+        <v>504986</v>
       </c>
       <c r="E138" t="n">
-        <v>5087</v>
+        <v>13285</v>
       </c>
       <c r="F138" t="n">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="G138" t="n">
-        <v>109450</v>
+        <v>95432</v>
+      </c>
+      <c r="H138" t="n">
+        <v>4.8125</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4144,25 +4580,28 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>17912</v>
+        <v>12013</v>
       </c>
       <c r="D139" t="n">
-        <v>934501</v>
+        <v>303855</v>
       </c>
       <c r="E139" t="n">
-        <v>8196</v>
+        <v>6608</v>
       </c>
       <c r="F139" t="n">
-        <v>369</v>
+        <v>250</v>
       </c>
       <c r="G139" t="n">
-        <v>118449</v>
+        <v>110500</v>
+      </c>
+      <c r="H139" t="n">
+        <v>9.198399999999999</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4171,25 +4610,28 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>15642</v>
+        <v>7726</v>
       </c>
       <c r="D140" t="n">
-        <v>376987</v>
+        <v>127751</v>
       </c>
       <c r="E140" t="n">
-        <v>6481</v>
+        <v>3428</v>
       </c>
       <c r="F140" t="n">
-        <v>275</v>
+        <v>119</v>
       </c>
       <c r="G140" t="n">
-        <v>101750</v>
+        <v>51289</v>
+      </c>
+      <c r="H140" t="n">
+        <v>6.6385</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4198,52 +4640,58 @@
         </is>
       </c>
       <c r="C141" t="n">
-        <v>7908</v>
+        <v>8715</v>
       </c>
       <c r="D141" t="n">
-        <v>102299</v>
+        <v>211257</v>
       </c>
       <c r="E141" t="n">
-        <v>2357</v>
+        <v>4019</v>
       </c>
       <c r="F141" t="n">
-        <v>184</v>
+        <v>213</v>
       </c>
       <c r="G141" t="n">
-        <v>93840</v>
+        <v>73911</v>
+      </c>
+      <c r="H141" t="n">
+        <v>8.4809</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-07-28</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>10392</v>
+        <v>11607</v>
       </c>
       <c r="D142" t="n">
-        <v>367025</v>
+        <v>274617</v>
       </c>
       <c r="E142" t="n">
-        <v>4206</v>
+        <v>3260</v>
       </c>
       <c r="F142" t="n">
-        <v>196</v>
+        <v>278</v>
       </c>
       <c r="G142" t="n">
-        <v>77224</v>
+        <v>96466</v>
+      </c>
+      <c r="H142" t="n">
+        <v>8.311</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4252,25 +4700,28 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>13769</v>
+        <v>14171</v>
       </c>
       <c r="D143" t="n">
-        <v>221733</v>
+        <v>713915</v>
       </c>
       <c r="E143" t="n">
-        <v>5891</v>
+        <v>10027</v>
       </c>
       <c r="F143" t="n">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="G143" t="n">
-        <v>92839</v>
+        <v>64588</v>
+      </c>
+      <c r="H143" t="n">
+        <v>4.5578</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4279,25 +4730,28 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>15077</v>
+        <v>11882</v>
       </c>
       <c r="D144" t="n">
-        <v>538961</v>
+        <v>389089</v>
       </c>
       <c r="E144" t="n">
-        <v>12960</v>
+        <v>8308</v>
       </c>
       <c r="F144" t="n">
-        <v>354</v>
+        <v>252</v>
       </c>
       <c r="G144" t="n">
-        <v>123900</v>
+        <v>77616</v>
+      </c>
+      <c r="H144" t="n">
+        <v>6.5322</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4306,25 +4760,28 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>12769</v>
+        <v>10358</v>
       </c>
       <c r="D145" t="n">
-        <v>441420</v>
+        <v>111996</v>
       </c>
       <c r="E145" t="n">
-        <v>7603</v>
+        <v>2171</v>
       </c>
       <c r="F145" t="n">
-        <v>215</v>
+        <v>122</v>
       </c>
       <c r="G145" t="n">
-        <v>73530</v>
+        <v>48068</v>
+      </c>
+      <c r="H145" t="n">
+        <v>4.6407</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4333,52 +4790,58 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>6930</v>
+        <v>12058</v>
       </c>
       <c r="D146" t="n">
-        <v>192741</v>
+        <v>226915</v>
       </c>
       <c r="E146" t="n">
-        <v>2641</v>
+        <v>5994</v>
       </c>
       <c r="F146" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="G146" t="n">
-        <v>86352</v>
+        <v>96525</v>
+      </c>
+      <c r="H146" t="n">
+        <v>8.005100000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>小红书</t>
+          <t>百度搜索</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-07-30</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>12482</v>
+        <v>11237</v>
       </c>
       <c r="D147" t="n">
-        <v>281796</v>
+        <v>246099</v>
       </c>
       <c r="E147" t="n">
-        <v>7809</v>
+        <v>5175</v>
       </c>
       <c r="F147" t="n">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="G147" t="n">
-        <v>117824</v>
+        <v>89804</v>
+      </c>
+      <c r="H147" t="n">
+        <v>7.9918</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>百度搜索</t>
+          <t>抖音信息流</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4387,25 +4850,28 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>12774</v>
+        <v>16362</v>
       </c>
       <c r="D148" t="n">
-        <v>171816</v>
+        <v>664332</v>
       </c>
       <c r="E148" t="n">
-        <v>5671</v>
+        <v>14209</v>
       </c>
       <c r="F148" t="n">
-        <v>275</v>
+        <v>212</v>
       </c>
       <c r="G148" t="n">
-        <v>113575</v>
+        <v>73352</v>
+      </c>
+      <c r="H148" t="n">
+        <v>4.4831</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>抖音信息流</t>
+          <t>微信朋友圈</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4414,25 +4880,28 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>17230</v>
+        <v>11010</v>
       </c>
       <c r="D149" t="n">
-        <v>768884</v>
+        <v>385455</v>
       </c>
       <c r="E149" t="n">
-        <v>14066</v>
+        <v>7984</v>
       </c>
       <c r="F149" t="n">
-        <v>326</v>
+        <v>213</v>
       </c>
       <c r="G149" t="n">
-        <v>115078</v>
+        <v>79023</v>
+      </c>
+      <c r="H149" t="n">
+        <v>7.1774</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>微信朋友圈</t>
+          <t>知乎广告</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4441,25 +4910,28 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>10876</v>
+        <v>11937</v>
       </c>
       <c r="D150" t="n">
-        <v>383683</v>
+        <v>182955</v>
       </c>
       <c r="E150" t="n">
-        <v>6478</v>
+        <v>2539</v>
       </c>
       <c r="F150" t="n">
-        <v>210</v>
+        <v>164</v>
       </c>
       <c r="G150" t="n">
-        <v>99330</v>
+        <v>70192</v>
+      </c>
+      <c r="H150" t="n">
+        <v>5.8802</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>知乎广告</t>
+          <t>小红书</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4468,46 +4940,22 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>6892</v>
+        <v>13317</v>
       </c>
       <c r="D151" t="n">
-        <v>141006</v>
+        <v>339160</v>
       </c>
       <c r="E151" t="n">
-        <v>2097</v>
+        <v>4955</v>
       </c>
       <c r="F151" t="n">
-        <v>118</v>
+        <v>268</v>
       </c>
       <c r="G151" t="n">
-        <v>49796</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>小红书</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>2024-07-30</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>9705</v>
-      </c>
-      <c r="D152" t="n">
-        <v>273408</v>
-      </c>
-      <c r="E152" t="n">
-        <v>6705</v>
-      </c>
-      <c r="F152" t="n">
-        <v>175</v>
-      </c>
-      <c r="G152" t="n">
-        <v>64225</v>
+        <v>131052</v>
+      </c>
+      <c r="H151" t="n">
+        <v>9.840999999999999</v>
       </c>
     </row>
   </sheetData>
